--- a/samples/test_data.xlsx
+++ b/samples/test_data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="R1be3558107ad4906904accfa11de4bdd"/>
+    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="Rfd23ae10888941b18976ba97e50783d8"/>
   </x:sheets>
 </x:workbook>
 </file>
